--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="R3b2f01b0212b49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="Rd2530d50b30e4578"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="Rd2530d50b30e4578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="R25d89783fabd41f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261027" sheetId="1" r:id="R25d89783fabd41f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="Rc763e25995a947d5"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="174">
-  <x:si>
-    <x:t>Daily Holdings (%)  10/27/2026</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="167">
+  <x:si>
+    <x:t>Daily Holdings (%)  10/28/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -58,13 +58,13 @@
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,326,450,226.76</x:t>
+    <x:t>$14,158,166,696.52</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.15%</x:t>
+    <x:t>19.56%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -79,10 +79,10 @@
     <x:t>15,707,426</x:t>
   </x:si>
   <x:si>
-    <x:t>$6,862,103,196.62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.65%</x:t>
+    <x:t>$6,903,570,801.26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.54%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -97,10 +97,10 @@
     <x:t>7,053,966</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,952,054,991.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.56%</x:t>
+    <x:t>$4,080,296,093.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.64%</x:t>
   </x:si>
   <x:si>
     <x:t>AVGO</x:t>
@@ -115,10 +115,10 @@
     <x:t>11,470,474</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,926,687,364.42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.52%</x:t>
+    <x:t>$4,035,427,457.94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.58%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -133,10 +133,28 @@
     <x:t>12,618,271</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,897,910,094.61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.48%</x:t>
+    <x:t>$3,909,518,903.93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.40%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Micron Technology Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000C5Z1S3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,576,442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,516,465,067.66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.86%</x:t>
   </x:si>
   <x:si>
     <x:t>ADI</x:t>
@@ -151,28 +169,10 @@
     <x:t>7,914,906</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,366,605,267.10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Micron Technology Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000C5Z1S3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,576,442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,321,656,271.92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.67%</x:t>
+    <x:t>$3,389,716,792.62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.68%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -187,10 +187,10 @@
     <x:t>13,114,799</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,194,371,592.43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.49%</x:t>
+    <x:t>$3,300,339,168.35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.56%</x:t>
   </x:si>
   <x:si>
     <x:t>ASML</x:t>
@@ -205,10 +205,28 @@
     <x:t>1,912,779</x:t>
   </x:si>
   <x:si>
-    <x:t>$3,128,483,949.03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.40%</x:t>
+    <x:t>$3,180,664,560.15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.39%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKHY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sk Hynix Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG0238L5JS9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,505,642</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,047,879,237.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.21%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -223,12 +241,30 @@
     <x:t>31,069,305</x:t>
   </x:si>
   <x:si>
-    <x:t>$2,912,436,650.70</x:t>
+    <x:t>$2,968,050,706.65</x:t>
   </x:si>
   <x:si>
     <x:t>4.10%</x:t>
   </x:si>
   <x:si>
+    <x:t>AMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Applied Materials Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BBPFB9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,040,262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,928,748,992.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.05%</x:t>
+  </x:si>
+  <x:si>
     <x:t>QCOM</x:t>
   </x:si>
   <x:si>
@@ -241,28 +277,10 @@
     <x:t>15,668,573</x:t>
   </x:si>
   <x:si>
-    <x:t>$2,885,681,089.41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.06%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Applied Materials Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BBPFB9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,040,262</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,787,450,933.66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.92%</x:t>
+    <x:t>$2,866,878,801.81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.96%</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -277,28 +295,7 @@
     <x:t>18,046,128</x:t>
   </x:si>
   <x:si>
-    <x:t>$2,772,968,028.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKHY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sk Hynix Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG0238L5JS9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,505,642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,689,980,121.12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.78%</x:t>
+    <x:t>$2,865,183,742.56</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -313,10 +310,10 @@
     <x:t>10,450,910</x:t>
   </x:si>
   <x:si>
-    <x:t>$2,517,101,673.50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.54%</x:t>
+    <x:t>$2,652,649,976.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.66%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -331,10 +328,10 @@
     <x:t>4,498,355</x:t>
   </x:si>
   <x:si>
-    <x:t>$1,543,295,633.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.17%</x:t>
+    <x:t>$1,540,506,653.30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.13%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -349,7 +346,7 @@
     <x:t>3,168,819</x:t>
   </x:si>
   <x:si>
-    <x:t>$1,503,351,109.98</x:t>
+    <x:t>$1,527,022,187.91</x:t>
   </x:si>
   <x:si>
     <x:t>2.11%</x:t>
@@ -367,10 +364,10 @@
     <x:t>3,309,232</x:t>
   </x:si>
   <x:si>
-    <x:t>$838,890,312.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.18%</x:t>
+    <x:t>$832,900,602.08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.15%</x:t>
   </x:si>
   <x:si>
     <x:t>MPWR</x:t>
@@ -385,10 +382,10 @@
     <x:t>683,819</x:t>
   </x:si>
   <x:si>
-    <x:t>$828,713,407.91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.17%</x:t>
+    <x:t>$828,255,249.18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.14%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -403,10 +400,10 @@
     <x:t>2,427,571</x:t>
   </x:si>
   <x:si>
-    <x:t>$785,756,181.28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.11%</x:t>
+    <x:t>$760,412,340.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.05%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -421,10 +418,10 @@
     <x:t>2,448,832</x:t>
   </x:si>
   <x:si>
-    <x:t>$702,055,646.08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.99%</x:t>
+    <x:t>$727,792,870.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.01%</x:t>
   </x:si>
   <x:si>
     <x:t>ARM</x:t>
@@ -439,10 +436,10 @@
     <x:t>3,015,158</x:t>
   </x:si>
   <x:si>
-    <x:t>$683,234,802.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.96%</x:t>
+    <x:t>$711,275,772.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.98%</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -457,10 +454,10 @@
     <x:t>13,231,026</x:t>
   </x:si>
   <x:si>
-    <x:t>$644,086,345.68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.91%</x:t>
+    <x:t>$641,969,381.52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.89%</x:t>
   </x:si>
   <x:si>
     <x:t>MCHP</x:t>
@@ -475,10 +472,10 @@
     <x:t>7,774,540</x:t>
   </x:si>
   <x:si>
-    <x:t>$623,284,871.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.88%</x:t>
+    <x:t>$619,086,620.20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.86%</x:t>
   </x:si>
   <x:si>
     <x:t>ON</x:t>
@@ -493,28 +490,10 @@
     <x:t>4,788,908</x:t>
   </x:si>
   <x:si>
-    <x:t>$376,743,392.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.53%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-USD CASH-</x:t>
-  </x:si>
-  <x:si>
-    <x:t> </x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,859,151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cash Bal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$43,859,150.99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.06%</x:t>
+    <x:t>$362,185,112.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.50%</x:t>
   </x:si>
   <x:si>
     <x:t>Other/Cash</x:t>
@@ -523,10 +502,10 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-13,579,851.57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-0.02%</x:t>
+    <x:t>$29,600,185.87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.04%</x:t>
   </x:si>
   <x:si>
     <x:t>These are not recommendations to buy or to sell any security. Securities and holdings may vary.</x:t>
@@ -600,10 +579,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:I31"/>
+  <x:dimension ref="A1:I30"/>
   <x:cols>
     <x:col min="1" max="1" width="12" customWidth="1"/>
-    <x:col min="2" max="2" width="16" customWidth="1"/>
+    <x:col min="2" max="2" width="12" customWidth="1"/>
     <x:col min="3" max="3" width="51" customWidth="1"/>
     <x:col min="4" max="4" width="25" customWidth="1"/>
     <x:col min="5" max="5" width="16" customWidth="1"/>
@@ -1103,7 +1082,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9" ht="15" customHeight="1">
@@ -1111,28 +1090,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
+      <x:c r="F18" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
+      <x:c r="H18" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="1" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H18" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I18" s="1" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15" customHeight="1">
@@ -1140,28 +1119,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
+      <x:c r="F19" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
+      <x:c r="H19" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="1" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="H19" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I19" s="1" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15" customHeight="1">
@@ -1169,28 +1148,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
+      <x:c r="F20" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
+      <x:c r="H20" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I20" s="1" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H20" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I20" s="1" t="s">
-        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9" ht="15" customHeight="1">
@@ -1198,28 +1177,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
+      <x:c r="F21" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
+      <x:c r="H21" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I21" s="1" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="H21" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I21" s="1" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9" ht="15" customHeight="1">
@@ -1227,28 +1206,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="F22" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
+      <x:c r="H22" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I22" s="1" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="H22" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I22" s="1" t="s">
-        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15" customHeight="1">
@@ -1256,28 +1235,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
+      <x:c r="F23" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
+      <x:c r="H23" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I23" s="1" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="H23" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I23" s="1" t="s">
-        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15" customHeight="1">
@@ -1285,28 +1264,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="E24" s="1" t="s">
+      <x:c r="F24" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
+      <x:c r="H24" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="1" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="H24" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I24" s="1" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15" customHeight="1">
@@ -1314,28 +1293,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
+      <x:c r="F25" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
+      <x:c r="H25" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="1" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I25" s="1" t="s">
-        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15" customHeight="1">
@@ -1343,28 +1322,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
+      <x:c r="F26" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
+      <x:c r="H26" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="1" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="H26" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I26" s="1" t="s">
-        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9" ht="15" customHeight="1">
@@ -1372,28 +1351,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="D27" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
+      <x:c r="F27" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
+      <x:c r="H27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I27" s="1" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9" ht="15" customHeight="1">
@@ -1401,28 +1380,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
+      <x:c r="D28" s="1" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
+      <x:c r="F28" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
+      <x:c r="H28" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="1" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I28" s="1" t="s">
-        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9" ht="15" customHeight="1">
@@ -1430,85 +1409,56 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="G29" s="1" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
+      <x:c r="H29" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F29" s="1" t="s">
+    </x:row>
+    <x:row r="30" spans="1:9" ht="15" customHeight="1">
+      <x:c r="A30" s="2" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I29" s="1" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:9" ht="15" customHeight="1">
-      <x:c r="A30" s="1">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="H30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I30" s="1" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:9" ht="15" customHeight="1">
-      <x:c r="A31" s="2" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H31" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I31" s="2" t="s">
+      <x:c r="B30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1516,7 +1466,7 @@
   <x:mergeCells count="3">
     <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A2:I2"/>
-    <x:mergeCell ref="A31:I31"/>
+    <x:mergeCell ref="A30:I30"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="Rc763e25995a947d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R91dcd093c650468c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R91dcd093c650468c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R3cc98f8297a949a3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R3cc98f8297a949a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R1e72b0bb33e846ce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="R1e72b0bb33e846ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="Rf5800125dbd043b5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-29.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="Rf5800125dbd043b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261028" sheetId="1" r:id="Receb7b89a0fc45c6"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="167">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <x:si>
     <x:t>Daily Holdings (%)  10/28/2026</x:t>
   </x:si>
@@ -52,13 +52,13 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>65,735,754</x:t>
+    <x:t>66,045,042</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,158,166,696.52</x:t>
+    <x:t>$14,224,781,145.96</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
@@ -76,10 +76,10 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,707,426</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,903,570,801.26</x:t>
+    <x:t>15,781,334</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,936,054,106.34</x:t>
   </x:si>
   <x:si>
     <x:t>9.54%</x:t>
@@ -94,10 +94,10 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>7,053,966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,080,296,093.04</x:t>
+    <x:t>7,087,158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$4,099,495,673.52</x:t>
   </x:si>
   <x:si>
     <x:t>5.64%</x:t>
@@ -112,10 +112,10 @@
     <x:t>BBG00KHY5S69</x:t>
   </x:si>
   <x:si>
-    <x:t>11,470,474</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$4,035,427,457.94</x:t>
+    <x:t>11,524,558</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$4,054,454,749.98</x:t>
   </x:si>
   <x:si>
     <x:t>5.58%</x:t>
@@ -130,10 +130,10 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,618,271</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,909,518,903.93</x:t>
+    <x:t>12,677,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,927,956,267.57</x:t>
   </x:si>
   <x:si>
     <x:t>5.40%</x:t>
@@ -148,10 +148,10 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,576,442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,516,465,067.66</x:t>
+    <x:t>3,593,266</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,533,006,929.18</x:t>
   </x:si>
   <x:si>
     <x:t>4.86%</x:t>
@@ -166,10 +166,10 @@
     <x:t>BBG000BB6G37</x:t>
   </x:si>
   <x:si>
-    <x:t>7,914,906</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,389,716,792.62</x:t>
+    <x:t>7,952,226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,405,699,829.02</x:t>
   </x:si>
   <x:si>
     <x:t>4.68%</x:t>
@@ -184,10 +184,10 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>13,114,799</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,300,339,168.35</x:t>
+    <x:t>13,176,503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,315,866,979.95</x:t>
   </x:si>
   <x:si>
     <x:t>4.56%</x:t>
@@ -202,10 +202,10 @@
     <x:t>BBG000K6MRN4</x:t>
   </x:si>
   <x:si>
-    <x:t>1,912,779</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,180,664,560.15</x:t>
+    <x:t>1,921,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,195,630,210.15</x:t>
   </x:si>
   <x:si>
     <x:t>4.39%</x:t>
@@ -220,10 +220,10 @@
     <x:t>BBG0238L5JS9</x:t>
   </x:si>
   <x:si>
-    <x:t>18,505,642</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,047,879,237.40</x:t>
+    <x:t>18,592,714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,062,219,995.80</x:t>
   </x:si>
   <x:si>
     <x:t>4.21%</x:t>
@@ -238,10 +238,10 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>31,069,305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,968,050,706.65</x:t>
+    <x:t>31,215,813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,982,046,615.89</x:t>
   </x:si>
   <x:si>
     <x:t>4.10%</x:t>
@@ -256,10 +256,10 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>7,040,262</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,928,748,992.00</x:t>
+    <x:t>7,073,466</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,942,561,856.00</x:t>
   </x:si>
   <x:si>
     <x:t>4.05%</x:t>
@@ -274,10 +274,10 @@
     <x:t>BBG000CGC1X8</x:t>
   </x:si>
   <x:si>
-    <x:t>15,668,573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,866,878,801.81</x:t>
+    <x:t>15,742,457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,880,397,357.29</x:t>
   </x:si>
   <x:si>
     <x:t>3.96%</x:t>
@@ -292,10 +292,10 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>18,046,128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,865,183,742.56</x:t>
+    <x:t>18,131,220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,878,693,799.40</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -307,10 +307,10 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,450,910</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,652,649,976.20</x:t>
+    <x:t>10,500,194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,665,159,241.08</x:t>
   </x:si>
   <x:si>
     <x:t>3.66%</x:t>
@@ -325,10 +325,10 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,498,355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,540,506,653.30</x:t>
+    <x:t>4,519,571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,547,772,284.66</x:t>
   </x:si>
   <x:si>
     <x:t>2.13%</x:t>
@@ -343,10 +343,10 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,168,819</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,527,022,187.91</x:t>
+    <x:t>3,183,759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,534,221,624.51</x:t>
   </x:si>
   <x:si>
     <x:t>2.11%</x:t>
@@ -361,10 +361,10 @@
     <x:t>BBG000BND699</x:t>
   </x:si>
   <x:si>
-    <x:t>3,309,232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$832,900,602.08</x:t>
+    <x:t>3,324,832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$836,826,966.08</x:t>
   </x:si>
   <x:si>
     <x:t>1.15%</x:t>
@@ -379,10 +379,10 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>683,819</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$828,255,249.18</x:t>
+    <x:t>687,047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$832,165,067.34</x:t>
   </x:si>
   <x:si>
     <x:t>1.14%</x:t>
@@ -397,10 +397,10 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,427,571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$760,412,340.04</x:t>
+    <x:t>2,439,019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$763,998,311.56</x:t>
   </x:si>
   <x:si>
     <x:t>1.05%</x:t>
@@ -415,10 +415,10 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,448,832</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$727,792,870.40</x:t>
+    <x:t>2,460,376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$731,223,747.20</x:t>
   </x:si>
   <x:si>
     <x:t>1.01%</x:t>
@@ -433,10 +433,10 @@
     <x:t>BBG01J1GXZF0</x:t>
   </x:si>
   <x:si>
-    <x:t>3,015,158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$711,275,772.20</x:t>
+    <x:t>3,029,378</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$714,630,270.20</x:t>
   </x:si>
   <x:si>
     <x:t>0.98%</x:t>
@@ -451,10 +451,10 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>13,231,026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$641,969,381.52</x:t>
+    <x:t>13,293,414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$644,996,447.28</x:t>
   </x:si>
   <x:si>
     <x:t>0.89%</x:t>
@@ -469,10 +469,10 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,774,540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$619,086,620.20</x:t>
+    <x:t>7,811,200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$622,005,856.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.86%</x:t>
@@ -487,25 +487,43 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,788,908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$362,185,112.04</x:t>
+    <x:t>4,811,492</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$363,893,139.96</x:t>
   </x:si>
   <x:si>
     <x:t>0.50%</x:t>
   </x:si>
   <x:si>
+    <x:t>-USD CASH-</x:t>
+  </x:si>
+  <x:si>
+    <x:t> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,116,698</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cash Bal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$45,116,698.02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.06%</x:t>
+  </x:si>
+  <x:si>
     <x:t>Other/Cash</x:t>
   </x:si>
   <x:si>
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$29,600,185.87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.04%</x:t>
+    <x:t>$-15,522,253.13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-0.02%</x:t>
   </x:si>
   <x:si>
     <x:t>These are not recommendations to buy or to sell any security. Securities and holdings may vary.</x:t>
@@ -579,10 +597,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:dimension ref="A1:I30"/>
+  <x:dimension ref="A1:I31"/>
   <x:cols>
     <x:col min="1" max="1" width="12" customWidth="1"/>
-    <x:col min="2" max="2" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="16" customWidth="1"/>
     <x:col min="3" max="3" width="51" customWidth="1"/>
     <x:col min="4" max="4" width="25" customWidth="1"/>
     <x:col min="5" max="5" width="16" customWidth="1"/>
@@ -1409,56 +1427,85 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15" customHeight="1">
-      <x:c r="A30" s="2" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="B30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H30" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I30" s="2" t="s">
+      <x:c r="A30" s="1">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="1" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9" ht="15" customHeight="1">
+      <x:c r="A31" s="2" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -1466,7 +1513,7 @@
   <x:mergeCells count="3">
     <x:mergeCell ref="A1:I1"/>
     <x:mergeCell ref="A2:I2"/>
-    <x:mergeCell ref="A30:I30"/>
+    <x:mergeCell ref="A31:I31"/>
   </x:mergeCells>
 </x:worksheet>
 </file>